--- a/SGC-CKN/Excel/c6f22531-e86b-4be2-924d-1b7674659d24_Thi_công_cọc_khoan_nhồi__tường_vây_cho_các_hạng_mục_Lô_CT-02_P1-48_D800_04-04-2026.xlsx
+++ b/SGC-CKN/Excel/c6f22531-e86b-4be2-924d-1b7674659d24_Thi_công_cọc_khoan_nhồi__tường_vây_cho_các_hạng_mục_Lô_CT-02_P1-48_D800_04-04-2026.xlsx
@@ -216,7 +216,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -289,12 +289,6 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
       <sz val="12"/>
       <name val="Arial"/>
     </font>
@@ -305,7 +299,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -375,11 +369,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5F3FC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC2626"/>
       </patternFill>
     </fill>
     <fill>
@@ -475,7 +464,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -567,16 +556,13 @@
     <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1165,16 +1151,16 @@
         <v>0</v>
       </c>
       <c r="G11" s="5">
-        <v>-3.4</v>
+        <v>-4</v>
       </c>
       <c r="H11" s="5">
         <v>0.5</v>
       </c>
       <c r="I11" s="5">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="J11" s="8">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>29</v>
@@ -1197,19 +1183,19 @@
         <v>32</v>
       </c>
       <c r="F12" s="9">
-        <v>-3.4</v>
+        <v>-4</v>
       </c>
       <c r="G12" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="H12" s="9">
         <v>0.67</v>
       </c>
       <c r="I12" s="9">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J12" s="12">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>29</v>
@@ -1232,7 +1218,7 @@
         <v>35</v>
       </c>
       <c r="F13" s="13">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="G13" s="13">
         <v>-9.2</v>
@@ -1241,10 +1227,10 @@
         <v>1</v>
       </c>
       <c r="I13" s="13">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="J13" s="12">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="K13" s="14" t="s">
         <v>29</v>
@@ -1410,35 +1396,35 @@
         <v>-39.9</v>
       </c>
       <c r="G18" s="28">
-        <v>-41.35</v>
+        <v>-44.35</v>
       </c>
       <c r="H18" s="28">
         <v>2</v>
       </c>
       <c r="I18" s="28">
-        <v>1.45</v>
-      </c>
-      <c r="J18" s="31">
-        <v>0.73</v>
+        <v>4.45</v>
+      </c>
+      <c r="J18" s="12">
+        <v>2.23</v>
       </c>
       <c r="K18" s="29" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="32" t="s">
+      <c r="A21" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="B21" s="32"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="32"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="32"/>
-      <c r="K21" s="32"/>
+      <c r="B21" s="31"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="31"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="31"/>
+      <c r="I21" s="31"/>
+      <c r="J21" s="31"/>
+      <c r="K21" s="31"/>
     </row>
     <row r="22" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1577,16 +1563,16 @@
         <v>0</v>
       </c>
       <c r="F2" s="5">
-        <v>-3.4</v>
+        <v>-4</v>
       </c>
       <c r="G2" s="5">
         <v>0.5</v>
       </c>
       <c r="H2" s="5">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="I2" s="8">
-        <v>6.8</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1603,19 +1589,19 @@
         <v>1</v>
       </c>
       <c r="E3" s="9">
-        <v>-3.4</v>
+        <v>-4</v>
       </c>
       <c r="F3" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="G3" s="9">
         <v>0.67</v>
       </c>
       <c r="H3" s="9">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="I3" s="12">
-        <v>2.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1632,7 +1618,7 @@
         <v>1</v>
       </c>
       <c r="E4" s="13">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="F4" s="13">
         <v>-9.2</v>
@@ -1641,10 +1627,10 @@
         <v>1</v>
       </c>
       <c r="H4" s="13">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="I4" s="12">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1780,45 +1766,45 @@
         <v>-39.9</v>
       </c>
       <c r="F9" s="28">
-        <v>-41.35</v>
+        <v>-44.35</v>
       </c>
       <c r="G9" s="28">
         <v>2</v>
       </c>
       <c r="H9" s="28">
-        <v>1.45</v>
-      </c>
-      <c r="I9" s="31">
-        <v>0.73</v>
+        <v>4.45</v>
+      </c>
+      <c r="I9" s="12">
+        <v>2.23</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="33" t="s">
+      <c r="A10" s="32" t="s">
         <v>62</v>
       </c>
-      <c r="B10" s="34" t="s">
+      <c r="B10" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="34" t="s">
+      <c r="C10" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="34">
+      <c r="D10" s="33">
         <v>8</v>
       </c>
-      <c r="E10" s="34">
+      <c r="E10" s="33">
         <v>0</v>
       </c>
-      <c r="F10" s="34">
-        <v>-41.35</v>
-      </c>
-      <c r="G10" s="34">
+      <c r="F10" s="33">
+        <v>-44.35</v>
+      </c>
+      <c r="G10" s="33">
         <v>7.33</v>
       </c>
-      <c r="H10" s="34">
-        <v>41.35</v>
-      </c>
-      <c r="I10" s="34">
-        <v>5.64</v>
+      <c r="H10" s="33">
+        <v>44.35</v>
+      </c>
+      <c r="I10" s="33">
+        <v>6.05</v>
       </c>
     </row>
   </sheetData>
